--- a/base-biosimilaires.xlsx
+++ b/base-biosimilaires.xlsx
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>652539</v>
+        <v>748081</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>1201</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1821,19 +1821,23 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>936311</v>
+        <v>943539</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>429</v>
@@ -2024,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U135"/>
+  <dimension ref="A1:U140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2303,8 +2307,16 @@
       <c r="I4" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
@@ -6556,47 +6568,49 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Nivestim</t>
+          <t>Ratiograstim</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Pfizer / Hospira</t>
+          <t>Teva / ratiopharm</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
+        <v>2008</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>153321</v>
+        <v>95542</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>15717675.14</v>
+        <v>11674935.7</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
-        <v>27</v>
-      </c>
+      <c r="P68" s="2" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr"/>
       <c r="S68" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
-          <t>PFIZER</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>3400949413379, 3400949413669, 3400949413720, 3400949413898, 3400949413959, 3400949501151, 3400949501465, 3400949501519</t>
+          <t>3400939981635, 3400939981864, 3400939981925, 3400939982007</t>
         </is>
       </c>
     </row>
@@ -6633,57 +6647,47 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Accofil</t>
+          <t>Nivestim</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Accord</t>
+          <t>Pfizer / Hospira</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>20026</v>
+        <v>153321</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>2444972.97</v>
-      </c>
-      <c r="O69" s="2" t="n">
-        <v>65</v>
-      </c>
+        <v>15717675.14</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr"/>
       <c r="P69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="2" t="n">
-        <v>54.62</v>
-      </c>
-      <c r="R69" s="2" t="n">
-        <v>52.5</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
       <c r="S69" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>VIATRIS MEDICA / ACCORD</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>3400930010419, 3400930010433, 3400930010457, 3400930010488, 3400930235485</t>
+          <t>3400949413379, 3400949413669, 3400949413720, 3400949413898, 3400949413959, 3400949501151, 3400949501465, 3400949501519</t>
         </is>
       </c>
     </row>
@@ -6720,29 +6724,59 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Grastofil</t>
+          <t>Accofil</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Accord / Apotex</t>
+          <t>Accord</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
-      <c r="U70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>20026</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>2444972.97</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>VIATRIS MEDICA / ACCORD</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>3400930010419, 3400930010433, 3400930010457, 3400930010488, 3400930235485</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6777,16 +6811,16 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Zefylti</t>
+          <t>Grastofil</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Accord / Apotex</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
@@ -6802,154 +6836,132 @@
       <c r="U71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>FILGRASTIM</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>L03AA02</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Soins de support (G-CSF)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Zefylti</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Stada</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>PEGFILGRASTIM</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>L03AA13</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Soins de support (G-CSF)</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>mixte</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>Princeps</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>Neulasta</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>Amgen</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="5" t="inlineStr"/>
-      <c r="K72" s="5" t="inlineStr"/>
-      <c r="L72" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M72" s="5" t="n">
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="5" t="inlineStr"/>
+      <c r="K73" s="5" t="inlineStr"/>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="n">
         <v>19155</v>
       </c>
-      <c r="N72" s="5" t="n">
+      <c r="N73" s="5" t="n">
         <v>11546905.47</v>
       </c>
-      <c r="O72" s="5" t="inlineStr"/>
-      <c r="P72" s="5" t="inlineStr"/>
-      <c r="Q72" s="5" t="inlineStr"/>
-      <c r="R72" s="5" t="inlineStr"/>
-      <c r="S72" s="5" t="n">
+      <c r="O73" s="5" t="inlineStr"/>
+      <c r="P73" s="5" t="inlineStr"/>
+      <c r="Q73" s="5" t="inlineStr"/>
+      <c r="R73" s="5" t="inlineStr"/>
+      <c r="S73" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="T72" s="5" t="inlineStr">
+      <c r="T73" s="5" t="inlineStr">
         <is>
           <t>AMGEN SAS</t>
         </is>
       </c>
-      <c r="U72" s="5" t="inlineStr">
+      <c r="U73" s="5" t="inlineStr">
         <is>
           <t>3400939535166</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>PEGFILGRASTIM</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>L03AA13</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Soins de support (G-CSF)</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>mixte</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Ziextenzo</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Sandoz</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>78974</v>
-      </c>
-      <c r="N73" s="2" t="n">
-        <v>32665041.81</v>
-      </c>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="2" t="inlineStr"/>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T73" s="2" t="inlineStr">
-        <is>
-          <t>SANDOZ</t>
-        </is>
-      </c>
-      <c r="U73" s="2" t="inlineStr">
-        <is>
-          <t>3400930162743</t>
         </is>
       </c>
     </row>
@@ -6986,47 +6998,49 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Pelgraz</t>
+          <t>Ziextenzo</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Accord</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>50407</v>
+        <v>78974</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>20972619.36</v>
+        <v>32665041.81</v>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="P74" s="2" t="inlineStr"/>
       <c r="Q74" s="2" t="inlineStr"/>
       <c r="R74" s="2" t="inlineStr"/>
       <c r="S74" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>ACCORD</t>
+          <t>SANDOZ</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>3400930157640, 3400930187951, 3400949500925</t>
+          <t>3400930162743</t>
         </is>
       </c>
     </row>
@@ -7063,12 +7077,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Pelmeg</t>
+          <t>Pelgraz</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Mundipharma / Cinfa</t>
+          <t>Accord</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
@@ -7082,14 +7096,14 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>44253</v>
+        <v>50407</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>18992607.15</v>
+        <v>20972619.36</v>
       </c>
       <c r="O75" s="2" t="inlineStr"/>
       <c r="P75" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
       <c r="R75" s="2" t="inlineStr"/>
@@ -7098,12 +7112,12 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>MUNDIPHARMA SAS</t>
+          <t>ACCORD</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>3400930163481, 3400949500826, 3400949501212, 3400949501335</t>
+          <t>3400930157640, 3400930187951, 3400949500925</t>
         </is>
       </c>
     </row>
@@ -7140,37 +7154,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Fulphila</t>
+          <t>Pelmeg</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Viatris / Biocon</t>
+          <t>Mundipharma / Cinfa</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>41213</v>
+        <v>44253</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>17551382.12</v>
+        <v>18992607.15</v>
       </c>
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr"/>
@@ -7179,12 +7189,12 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>BIOCON BIOLOGICS</t>
+          <t>MUNDIPHARMA SAS</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>3400930163245, 3400949501571</t>
+          <t>3400930163481, 3400949500826, 3400949501212, 3400949501335</t>
         </is>
       </c>
     </row>
@@ -7221,22 +7231,18 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Grasustek</t>
+          <t>Fulphila</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Mundipharma</t>
+          <t>Viatris / Biocon</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
@@ -7248,34 +7254,28 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>22336</v>
+        <v>41213</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>9539043.109999999</v>
-      </c>
-      <c r="O77" s="2" t="n">
-        <v>187</v>
-      </c>
+        <v>17551382.12</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr"/>
       <c r="P77" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q77" s="2" t="n">
-        <v>363.4</v>
-      </c>
-      <c r="R77" s="2" t="n">
-        <v>349.26</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
       <c r="S77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>ZENTIVA FRANCE</t>
+          <t>BIOCON BIOLOGICS</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>3400930203538</t>
+          <t>3400930163245, 3400949501571</t>
         </is>
       </c>
     </row>
@@ -7312,45 +7312,61 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Nyvepria</t>
+          <t>Grasustek</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Mundipharma</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
+        <v>2019</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3326</v>
+        <v>22336</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>1394125.59</v>
-      </c>
-      <c r="O78" s="2" t="inlineStr"/>
+        <v>9539043.109999999</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>187</v>
+      </c>
       <c r="P78" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>349.26</v>
+      </c>
+      <c r="S78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" s="2" t="inlineStr"/>
-      <c r="R78" s="2" t="inlineStr"/>
-      <c r="S78" s="2" t="inlineStr"/>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>PFIZER</t>
+          <t>ZENTIVA FRANCE</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>3400930216279</t>
+          <t>3400930203538</t>
         </is>
       </c>
     </row>
@@ -7387,12 +7403,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Cegfila</t>
+          <t>Nyvepria</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Mundipharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
@@ -7406,26 +7422,26 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>48121</v>
+        <v>3326</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>20035367.92</v>
+        <v>1394125.59</v>
       </c>
       <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="2" t="inlineStr"/>
-      <c r="S79" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="S79" s="2" t="inlineStr"/>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>MUNDIPHARMA SAS</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>3400930202029</t>
+          <t>3400930216279</t>
         </is>
       </c>
     </row>
@@ -7462,53 +7478,45 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Stimufend</t>
+          <t>Cegfila</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Mundipharma</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>16511</v>
+        <v>48121</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>6881403.55</v>
+        <v>20035367.92</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr"/>
       <c r="Q80" s="2" t="inlineStr"/>
       <c r="R80" s="2" t="inlineStr"/>
       <c r="S80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>TEVA SANTE / FRESENIUS KABI</t>
+          <t>MUNDIPHARMA SAS</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>3400930249161</t>
+          <t>3400930202029</t>
         </is>
       </c>
     </row>
@@ -7545,29 +7553,55 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Udenyca</t>
+          <t>Stimufend</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Accord / Coherus</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
+        <v>2022</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>16511</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>6881403.55</v>
+      </c>
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr"/>
       <c r="Q81" s="2" t="inlineStr"/>
       <c r="R81" s="2" t="inlineStr"/>
-      <c r="S81" s="2" t="inlineStr"/>
-      <c r="T81" s="2" t="inlineStr"/>
-      <c r="U81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>TEVA SANTE / FRESENIUS KABI</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>3400930249161</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -7602,16 +7636,16 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Dyrupeg</t>
+          <t>Udenyca</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Accord / Coherus</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
@@ -7627,170 +7661,140 @@
       <c r="U82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>PEGFILGRASTIM</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>L03AA13</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Soins de support (G-CSF)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Dyrupeg</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Stada</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>EPOETINE</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>B03XA01</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>Anémie (IRC / chimio)</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>mixte</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>Princeps</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>Eprex</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>Janssen / J&amp;J</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="5" t="inlineStr"/>
-      <c r="K83" s="5" t="inlineStr"/>
-      <c r="L83" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M83" s="5" t="n">
+      <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="5" t="inlineStr"/>
+      <c r="K84" s="5" t="inlineStr"/>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="n">
         <v>67674</v>
       </c>
-      <c r="N83" s="5" t="n">
+      <c r="N84" s="5" t="n">
         <v>10577324.34</v>
       </c>
-      <c r="O83" s="5" t="n">
+      <c r="O84" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="P83" s="5" t="n">
+      <c r="P84" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="Q83" s="5" t="n">
+      <c r="Q84" s="5" t="n">
         <v>164.46</v>
       </c>
-      <c r="R83" s="5" t="n">
+      <c r="R84" s="5" t="n">
         <v>158.06</v>
       </c>
-      <c r="S83" s="5" t="n">
+      <c r="S84" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="T83" s="5" t="inlineStr">
+      <c r="T84" s="5" t="inlineStr">
         <is>
           <t>JANSSEN CILAG</t>
         </is>
       </c>
-      <c r="U83" s="5" t="inlineStr">
+      <c r="U84" s="5" t="inlineStr">
         <is>
           <t>3400936992368, 3400934931215, 3400935497031, 3400935497260, 3400935497499, 3400936466654, 3400936466715, 3400936466883, 3400936466944, 3400936991996, 3400938327649</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>EPOETINE</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>B03XA01</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Anémie (IRC / chimio)</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>mixte</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Binocrit</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Sandoz</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>458362</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>63759350.54</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>475</v>
-      </c>
-      <c r="P84" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q84" s="2" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="R84" s="2" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="S84" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="T84" s="2" t="inlineStr">
-        <is>
-          <t>SANDOZ</t>
-        </is>
-      </c>
-      <c r="U84" s="2" t="inlineStr">
-        <is>
-          <t>3400949818518, 3400938214765, 3400938214994, 3400938215137, 3400938215427, 3400938215656, 3400938215885, 3400938216318, 3400938216776, 3400938216837, 3400949501601, 3400949818396, 3400949818747</t>
         </is>
       </c>
     </row>
@@ -7827,29 +7831,59 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Abseamed</t>
+          <t>Binocrit</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Medice</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
         <v>2007</v>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr"/>
-      <c r="O85" s="2" t="inlineStr"/>
-      <c r="P85" s="2" t="inlineStr"/>
-      <c r="Q85" s="2" t="inlineStr"/>
-      <c r="R85" s="2" t="inlineStr"/>
-      <c r="S85" s="2" t="inlineStr"/>
-      <c r="T85" s="2" t="inlineStr"/>
-      <c r="U85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>458362</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>63759350.54</v>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="P85" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="S85" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>SANDOZ</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>3400949818518, 3400938214765, 3400938214994, 3400938215137, 3400938215427, 3400938215656, 3400938215885, 3400938216318, 3400938216776, 3400938216837, 3400949501601, 3400949818396, 3400949818747</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -7884,12 +7918,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Retacrit</t>
+          <t>Abseamed</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Pfizer / Hospira</t>
+          <t>Medice</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
@@ -7897,42 +7931,16 @@
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>220430</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>31676971.27</v>
-      </c>
-      <c r="O86" s="2" t="n">
-        <v>410</v>
-      </c>
-      <c r="P86" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q86" s="2" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="R86" s="2" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="S86" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" s="2" t="inlineStr">
-        <is>
-          <t>PFIZER</t>
-        </is>
-      </c>
-      <c r="U86" s="2" t="inlineStr">
-        <is>
-          <t>3400930012208, 3400930012215, 3400930012109, 3400930012116, 3400930012123, 3400930012130, 3400930012147, 3400930012154, 3400930012178, 3400930012192, 3400930012093</t>
-        </is>
-      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -7967,12 +7975,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Silapo</t>
+          <t>Retacrit</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Pfizer / Hospira</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
@@ -7980,176 +7988,178 @@
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
-      <c r="N87" s="2" t="inlineStr"/>
-      <c r="O87" s="2" t="inlineStr"/>
-      <c r="P87" s="2" t="inlineStr"/>
-      <c r="Q87" s="2" t="inlineStr"/>
-      <c r="R87" s="2" t="inlineStr"/>
-      <c r="S87" s="2" t="inlineStr"/>
-      <c r="T87" s="2" t="inlineStr"/>
-      <c r="U87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>220430</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>31676971.27</v>
+      </c>
+      <c r="O87" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="S87" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>PFIZER</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>3400930012208, 3400930012215, 3400930012109, 3400930012116, 3400930012123, 3400930012130, 3400930012147, 3400930012154, 3400930012178, 3400930012192, 3400930012093</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>EPOETINE</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>B03XA01</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Anémie (IRC / chimio)</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Silapo</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Stada</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>INSULINE GLARGINE</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>A10AE04</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>Diabète</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>mixte</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>Princeps</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>Lantus</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>Sanofi</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
-      <c r="K88" s="5" t="inlineStr"/>
-      <c r="L88" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M88" s="5" t="n">
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="5" t="inlineStr"/>
+      <c r="K89" s="5" t="inlineStr"/>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="n">
         <v>1335792</v>
       </c>
-      <c r="N88" s="5" t="n">
+      <c r="N89" s="5" t="n">
         <v>50276627.89</v>
       </c>
-      <c r="O88" s="5" t="n">
+      <c r="O89" s="5" t="n">
         <v>4475</v>
       </c>
-      <c r="P88" s="5" t="n">
+      <c r="P89" s="5" t="n">
         <v>227</v>
       </c>
-      <c r="Q88" s="5" t="n">
+      <c r="Q89" s="5" t="n">
         <v>33.59</v>
       </c>
-      <c r="R88" s="5" t="n">
+      <c r="R89" s="5" t="n">
         <v>32.28</v>
       </c>
-      <c r="S88" s="5" t="n">
+      <c r="S89" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="T88" s="5" t="inlineStr">
+      <c r="T89" s="5" t="inlineStr">
         <is>
           <t>SANOFI AVENTI.F</t>
         </is>
       </c>
-      <c r="U88" s="5" t="inlineStr">
+      <c r="U89" s="5" t="inlineStr">
         <is>
           <t>3400937722988, 3400935463203, 3400935946492</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>INSULINE GLARGINE</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>A10AE04</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Diabète</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>mixte</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Abasaglar</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Lilly / Boehringer</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>1505207</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>54334714.92</v>
-      </c>
-      <c r="O89" s="2" t="n">
-        <v>7794</v>
-      </c>
-      <c r="P89" s="2" t="inlineStr"/>
-      <c r="Q89" s="2" t="n">
-        <v>31.19</v>
-      </c>
-      <c r="R89" s="2" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="S89" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="T89" s="2" t="inlineStr">
-        <is>
-          <t>LILLY FRANCE</t>
-        </is>
-      </c>
-      <c r="U89" s="2" t="inlineStr">
-        <is>
-          <t>3400930040072, 3400930016169</t>
         </is>
       </c>
     </row>
@@ -8186,183 +8196,207 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
+          <t>Abasaglar</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Lilly / Boehringer</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>1505207</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>54334714.92</v>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v>7794</v>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="n">
+        <v>31.19</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="S90" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>LILLY FRANCE</t>
+        </is>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>3400930040072, 3400930016169</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>INSULINE GLARGINE</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>A10AE04</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Diabète</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
           <t>Semglee</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Viatris / Biocon</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
+      <c r="I91" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="n">
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" s="2" t="inlineStr"/>
-      <c r="R90" s="2" t="inlineStr"/>
-      <c r="S90" s="2" t="inlineStr"/>
-      <c r="T90" s="2" t="inlineStr">
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr">
         <is>
           <t>BIOCON BIOLOGICS</t>
         </is>
       </c>
-      <c r="U90" s="2" t="inlineStr">
+      <c r="U91" s="2" t="inlineStr">
         <is>
           <t>3400930270356</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>INSULINE ASPARTE</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>A10AB05</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Diabète</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>mixte</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>Princeps</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>NovoRapid</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H92" s="5" t="inlineStr">
         <is>
           <t>Novo Nordisk</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="5" t="inlineStr"/>
-      <c r="K91" s="5" t="inlineStr"/>
-      <c r="L91" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M91" s="5" t="n">
+      <c r="I92" s="5" t="inlineStr"/>
+      <c r="J92" s="5" t="inlineStr"/>
+      <c r="K92" s="5" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="n">
         <v>3613469</v>
       </c>
-      <c r="N91" s="5" t="n">
+      <c r="N92" s="5" t="n">
         <v>74809914.33</v>
       </c>
-      <c r="O91" s="5" t="n">
+      <c r="O92" s="5" t="n">
         <v>3768</v>
       </c>
-      <c r="P91" s="5" t="inlineStr"/>
-      <c r="Q91" s="5" t="n">
+      <c r="P92" s="5" t="inlineStr"/>
+      <c r="Q92" s="5" t="n">
         <v>11.78</v>
       </c>
-      <c r="R91" s="5" t="n">
+      <c r="R92" s="5" t="n">
         <v>11.32</v>
       </c>
-      <c r="S91" s="5" t="n">
+      <c r="S92" s="5" t="n">
         <v>186</v>
       </c>
-      <c r="T91" s="5" t="inlineStr">
+      <c r="T92" s="5" t="inlineStr">
         <is>
           <t>NOVO NORDISK</t>
         </is>
       </c>
-      <c r="U91" s="5" t="inlineStr">
+      <c r="U92" s="5" t="inlineStr">
         <is>
           <t>3400935527400, 3400935259097, 3400927714573, 3400935259219</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>INSULINE ASPARTE</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>A10AB05</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Diabète</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>mixte</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Insuline asparte Sanofi</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Sanofi</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
-      <c r="S92" s="2" t="inlineStr"/>
-      <c r="T92" s="2" t="inlineStr"/>
-      <c r="U92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -8397,23 +8431,19 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Kirsty</t>
+          <t>Insuline asparte Sanofi</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Viatris / Biocon</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr"/>
@@ -8426,296 +8456,280 @@
       <c r="U93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>INSULINE ASPARTE</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>A10AB05</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Diabète</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Kirsty</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Viatris / Biocon</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>INSULINE LISPRO</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>A10AB04</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>Diabète</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>mixte</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>Princeps</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>Humalog</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>Lilly</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="5" t="inlineStr"/>
-      <c r="K94" s="5" t="inlineStr"/>
-      <c r="L94" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M94" s="5" t="n">
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="5" t="inlineStr"/>
+      <c r="K95" s="5" t="inlineStr"/>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="n">
         <v>1907590</v>
       </c>
-      <c r="N94" s="5" t="n">
+      <c r="N95" s="5" t="n">
         <v>52641546.96</v>
       </c>
-      <c r="O94" s="5" t="n">
+      <c r="O95" s="5" t="n">
         <v>4815</v>
       </c>
-      <c r="P94" s="5" t="n">
+      <c r="P95" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="Q94" s="5" t="n">
+      <c r="Q95" s="5" t="n">
         <v>13.14</v>
       </c>
-      <c r="R94" s="5" t="n">
+      <c r="R95" s="5" t="n">
         <v>12.63</v>
       </c>
-      <c r="S94" s="5" t="n">
+      <c r="S95" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="T94" s="5" t="inlineStr">
+      <c r="T95" s="5" t="inlineStr">
         <is>
           <t>LILLY FRANCE</t>
         </is>
       </c>
-      <c r="U94" s="5" t="inlineStr">
+      <c r="U95" s="5" t="inlineStr">
         <is>
           <t>3400938510980, 3400934142680, 3400930000854, 3400938511062, 3400938511123, 3400930125267, 3400934373930, 3400934944512, 3400934944680</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>INSULINE LISPRO</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>A10AB04</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Diabète</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>mixte</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Biosimilaire</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>Insuline lispro Sanofi</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Sanofi</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
+      <c r="I96" s="2" t="n">
         <v>2017</v>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
-      <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" s="2" t="inlineStr"/>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr"/>
-      <c r="S95" s="2" t="inlineStr"/>
-      <c r="T95" s="2" t="inlineStr"/>
-      <c r="U95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>RANIBIZUMAB</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>S01LA04</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Ophtalmo (intravitréen)</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>hopital</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr">
         <is>
           <t>Princeps</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>Lucentis</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="H97" s="5" t="inlineStr">
         <is>
           <t>Novartis / Genentech</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr"/>
-      <c r="K96" s="5" t="inlineStr"/>
-      <c r="L96" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M96" s="5" t="n">
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="5" t="inlineStr"/>
+      <c r="K97" s="5" t="inlineStr"/>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M97" s="5" t="n">
         <v>339820</v>
       </c>
-      <c r="N96" s="5" t="n">
+      <c r="N97" s="5" t="n">
         <v>144160943.91</v>
       </c>
-      <c r="O96" s="5" t="n">
+      <c r="O97" s="5" t="n">
         <v>1050</v>
       </c>
-      <c r="P96" s="5" t="inlineStr"/>
-      <c r="Q96" s="5" t="n">
+      <c r="P97" s="5" t="inlineStr"/>
+      <c r="Q97" s="5" t="n">
         <v>288.45</v>
       </c>
-      <c r="R96" s="5" t="n">
+      <c r="R97" s="5" t="n">
         <v>277.23</v>
       </c>
-      <c r="S96" s="5" t="n">
+      <c r="S97" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="T96" s="5" t="inlineStr">
+      <c r="T97" s="5" t="inlineStr">
         <is>
           <t>NOVARTIS PHARMA</t>
         </is>
       </c>
-      <c r="U96" s="5" t="inlineStr">
+      <c r="U97" s="5" t="inlineStr">
         <is>
           <t>3400927671197</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>RANIBIZUMAB</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>S01LA04</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Ophtalmo (intravitréen)</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>hopital</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Byooviz</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Biogen / Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>12920</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>4212491.58</v>
-      </c>
-      <c r="O97" s="2" t="inlineStr"/>
-      <c r="P97" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="2" t="inlineStr"/>
-      <c r="S97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T97" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG BIOEPIS NL B.V.</t>
-        </is>
-      </c>
-      <c r="U97" s="2" t="inlineStr">
-        <is>
-          <t>3400930278048</t>
         </is>
       </c>
     </row>
@@ -8752,53 +8766,47 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Ranivisio</t>
+          <t>Byooviz</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Teva / Bioeq</t>
+          <t>Biogen / Samsung Bioepis</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>40364</v>
+        <v>12920</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>13125673.42</v>
+        <v>4212491.58</v>
       </c>
       <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr"/>
       <c r="S98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>TEVA SANTE</t>
+          <t>SAMSUNG BIOEPIS NL B.V.</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>3400930258675, 3400930320396</t>
+          <t>3400930278048</t>
         </is>
       </c>
     </row>
@@ -8835,12 +8843,12 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Ximluci</t>
+          <t>Ranivisio</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Stada / Xbrane</t>
+          <t>Teva / Bioeq</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
@@ -8862,125 +8870,119 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>562</v>
+        <v>40364</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>179685.2</v>
+        <v>13125673.42</v>
       </c>
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr"/>
       <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr"/>
-      <c r="S99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
+          <t>TEVA SANTE</t>
+        </is>
+      </c>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>3400930258675, 3400930320396</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>RANIBIZUMAB</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>S01LA04</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Ophtalmo (intravitréen)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>hopital</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Ximluci</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Stada / Xbrane</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>179685.2</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
           <t>EG LABO</t>
         </is>
       </c>
-      <c r="U99" s="2" t="inlineStr">
+      <c r="U100" s="2" t="inlineStr">
         <is>
           <t>3400930266922</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>AFLIBERCEPT</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>S01LA05</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Ophtalmo (intravitréen)</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>hopital</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>Princeps</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>Eylea 2 mg</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>Bayer / Regeneron</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr"/>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L100" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v>992783</v>
-      </c>
-      <c r="N100" s="5" t="n">
-        <v>605709419.33</v>
-      </c>
-      <c r="O100" s="5" t="n">
-        <v>5992</v>
-      </c>
-      <c r="P100" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q100" s="5" t="n">
-        <v>312.4</v>
-      </c>
-      <c r="R100" s="5" t="n">
-        <v>300.25</v>
-      </c>
-      <c r="S100" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="T100" s="5" t="inlineStr">
-        <is>
-          <t>BAYER HEALTHCAR</t>
-        </is>
-      </c>
-      <c r="U100" s="5" t="inlineStr">
-        <is>
-          <t>3400930303122, 3400926783501, 3400926783679, 3400930283325</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AFLIBERCEPT</t>
+          <t>RANIBIZUMAB</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>S01LA05</t>
+          <t>S01LA04</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -9005,110 +9007,132 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Afqlir</t>
+          <t>Rimmyrah</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Lupin</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="M101" s="2" t="n">
-        <v>603</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>234705.69</v>
-      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>
       <c r="R101" s="2" t="inlineStr"/>
-      <c r="S101" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="S101" s="2" t="inlineStr"/>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>SANDOZ</t>
+          <t>ORION PHARMA</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>3400930306567</t>
+          <t>3400930283967</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>AFLIBERCEPT</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>S01LA05</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>Ophtalmo (intravitréen)</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>hopital</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Yesafili</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="inlineStr"/>
-      <c r="Q102" s="2" t="inlineStr"/>
-      <c r="R102" s="2" t="inlineStr"/>
-      <c r="S102" s="2" t="inlineStr"/>
-      <c r="T102" s="2" t="inlineStr"/>
-      <c r="U102" s="2" t="inlineStr"/>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Princeps</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Eylea 2 mg</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Bayer / Regeneron</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr"/>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="n">
+        <v>992783</v>
+      </c>
+      <c r="N102" s="5" t="n">
+        <v>605709419.33</v>
+      </c>
+      <c r="O102" s="5" t="n">
+        <v>5992</v>
+      </c>
+      <c r="P102" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q102" s="5" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="R102" s="5" t="n">
+        <v>300.25</v>
+      </c>
+      <c r="S102" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="T102" s="5" t="inlineStr">
+        <is>
+          <t>BAYER HEALTHCAR</t>
+        </is>
+      </c>
+      <c r="U102" s="5" t="inlineStr">
+        <is>
+          <t>3400930303122, 3400926783501, 3400926783679, 3400930283325</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -9143,29 +9167,53 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Opuviz</t>
+          <t>Afqlir</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Biogen / Samsung Bioepis</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>234705.69</v>
+      </c>
       <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="2" t="inlineStr"/>
-      <c r="S103" s="2" t="inlineStr"/>
-      <c r="T103" s="2" t="inlineStr"/>
-      <c r="U103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>SANDOZ</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>3400930306567</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -9200,16 +9248,16 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Eydenzelt</t>
+          <t>Yesafili</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
@@ -9257,43 +9305,29 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Pavblu</t>
+          <t>Opuviz</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Biogen / Samsung Bioepis</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr"/>
-      <c r="P105" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P105" s="2" t="inlineStr"/>
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr"/>
       <c r="S105" s="2" t="inlineStr"/>
-      <c r="T105" s="2" t="inlineStr">
-        <is>
-          <t>AMGEN SAS</t>
-        </is>
-      </c>
-      <c r="U105" s="2" t="inlineStr">
-        <is>
-          <t>3400930313176</t>
-        </is>
-      </c>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -9328,12 +9362,12 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Mynzepli</t>
+          <t>Eydenzelt</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Advanz / Alvotech</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
@@ -9385,12 +9419,12 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Ahzantive</t>
+          <t>Pavblu</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Formycon / Klinge</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
@@ -9398,259 +9432,223 @@
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr"/>
-      <c r="P107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q107" s="2" t="inlineStr"/>
       <c r="R107" s="2" t="inlineStr"/>
       <c r="S107" s="2" t="inlineStr"/>
-      <c r="T107" s="2" t="inlineStr"/>
-      <c r="U107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>AMGEN SAS</t>
+        </is>
+      </c>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>3400930313176</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>TERIPARATIDE</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>H05AA02</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>Ostéoporose</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>ville</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>Princeps</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>Forstéo</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>Lilly</t>
-        </is>
-      </c>
-      <c r="I108" s="5" t="inlineStr"/>
-      <c r="J108" s="5" t="inlineStr"/>
-      <c r="K108" s="5" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M108" s="5" t="n">
-        <v>19448</v>
-      </c>
-      <c r="N108" s="5" t="n">
-        <v>3972548.03</v>
-      </c>
-      <c r="O108" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="P108" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q108" s="5" t="n">
-        <v>189.02</v>
-      </c>
-      <c r="R108" s="5" t="n">
-        <v>181.67</v>
-      </c>
-      <c r="S108" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" s="5" t="inlineStr">
-        <is>
-          <t>LILLY FRANCE</t>
-        </is>
-      </c>
-      <c r="U108" s="5" t="inlineStr">
-        <is>
-          <t>3400936221628</t>
-        </is>
-      </c>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>AFLIBERCEPT</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>S01LA05</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Ophtalmo (intravitréen)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>hopital</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Mynzepli</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Advanz / Alvotech</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>AFLIBERCEPT</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>S01LA05</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Ophtalmo (intravitréen)</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>hopital</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Ahzantive</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Formycon / Klinge</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
           <t>TERIPARATIDE</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>H05AA02</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>Ostéoporose</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
         <is>
           <t>ville</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Movymia</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Stada</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>49144</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>9814975.189999999</v>
-      </c>
-      <c r="O109" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="P109" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q109" s="2" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="R109" s="2" t="inlineStr"/>
-      <c r="S109" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T109" s="2" t="inlineStr">
-        <is>
-          <t>EG LABO / EG</t>
-        </is>
-      </c>
-      <c r="U109" s="2" t="inlineStr">
-        <is>
-          <t>3400930119310, 3615840000065</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>TERIPARATIDE</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>H05AA02</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Ostéoporose</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>ville</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Terrosa</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Gedeon Richter</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>22483</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>4481793.51</v>
-      </c>
-      <c r="O110" s="2" t="inlineStr"/>
-      <c r="P110" s="2" t="inlineStr"/>
-      <c r="Q110" s="2" t="inlineStr"/>
-      <c r="R110" s="2" t="inlineStr"/>
-      <c r="S110" s="2" t="n">
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Princeps</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Forstéo</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>Lilly</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr"/>
+      <c r="J110" s="5" t="inlineStr"/>
+      <c r="K110" s="5" t="inlineStr"/>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="n">
+        <v>19448</v>
+      </c>
+      <c r="N110" s="5" t="n">
+        <v>3972548.03</v>
+      </c>
+      <c r="O110" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P110" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q110" s="5" t="n">
+        <v>189.02</v>
+      </c>
+      <c r="R110" s="5" t="n">
+        <v>181.67</v>
+      </c>
+      <c r="S110" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="T110" s="2" t="inlineStr">
-        <is>
-          <t>ARROW GENERIQUE</t>
-        </is>
-      </c>
-      <c r="U110" s="2" t="inlineStr">
-        <is>
-          <t>3400930271162</t>
+      <c r="T110" s="5" t="inlineStr">
+        <is>
+          <t>LILLY FRANCE</t>
+        </is>
+      </c>
+      <c r="U110" s="5" t="inlineStr">
+        <is>
+          <t>3400936221628</t>
         </is>
       </c>
     </row>
@@ -9687,45 +9685,59 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Livogiva</t>
+          <t>Movymia</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Theramex</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="2" t="inlineStr"/>
+        <v>2017</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>10458</v>
+        <v>49144</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>2090928.92</v>
-      </c>
-      <c r="O111" s="2" t="inlineStr"/>
-      <c r="P111" s="2" t="inlineStr"/>
-      <c r="Q111" s="2" t="inlineStr"/>
+        <v>9814975.189999999</v>
+      </c>
+      <c r="O111" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="P111" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q111" s="2" t="n">
+        <v>41.2</v>
+      </c>
       <c r="R111" s="2" t="inlineStr"/>
       <c r="S111" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>THERAMEX FRANCE</t>
+          <t>EG LABO / EG</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
         <is>
-          <t>3400930212271</t>
+          <t>3400930119310, 3615840000065</t>
         </is>
       </c>
     </row>
@@ -9762,16 +9774,16 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Sondelbay</t>
+          <t>Terrosa</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Accord</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
@@ -9781,10 +9793,10 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>9239</v>
+        <v>22483</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>1841762.16</v>
+        <v>4481793.51</v>
       </c>
       <c r="O112" s="2" t="inlineStr"/>
       <c r="P112" s="2" t="inlineStr"/>
@@ -9795,12 +9807,12 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>ACCORD</t>
+          <t>ARROW GENERIQUE</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
         <is>
-          <t>3400930248256</t>
+          <t>3400930271162</t>
         </is>
       </c>
     </row>
@@ -9837,135 +9849,147 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Kauliv</t>
+          <t>Livogiva</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Theramex / Strides</t>
+          <t>Theramex</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>10458</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>2090928.92</v>
+      </c>
       <c r="O113" s="2" t="inlineStr"/>
       <c r="P113" s="2" t="inlineStr"/>
       <c r="Q113" s="2" t="inlineStr"/>
       <c r="R113" s="2" t="inlineStr"/>
-      <c r="S113" s="2" t="inlineStr"/>
-      <c r="T113" s="2" t="inlineStr"/>
-      <c r="U113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>THERAMEX FRANCE</t>
+        </is>
+      </c>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
+          <t>3400930212271</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>DENOSUMAB</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>M05BX04</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>Os / oncologie</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>mixte</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>Princeps</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>Prolia / Xgeva</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr"/>
-      <c r="J114" s="5" t="inlineStr"/>
-      <c r="K114" s="5" t="inlineStr"/>
-      <c r="L114" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v>333737</v>
-      </c>
-      <c r="N114" s="5" t="n">
-        <v>72539859.55</v>
-      </c>
-      <c r="O114" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="P114" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q114" s="5" t="n">
-        <v>144.79</v>
-      </c>
-      <c r="R114" s="5" t="n">
-        <v>139.16</v>
-      </c>
-      <c r="S114" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="T114" s="5" t="inlineStr">
-        <is>
-          <t>AMGEN SAS</t>
-        </is>
-      </c>
-      <c r="U114" s="5" t="inlineStr">
-        <is>
-          <t>3400949285785, 3400921725384, 3400930289907</t>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>TERIPARATIDE</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>H05AA02</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Ostéoporose</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>ville</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Sondelbay</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Accord</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>9239</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>1841762.16</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>ACCORD</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>3400930248256</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>DENOSUMAB</t>
+          <t>TERIPARATIDE</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>M05BX04</t>
+          <t>H05AA02</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Os / oncologie</t>
+          <t>Ostéoporose</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>OUI</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>mixte</t>
+          <t>ville</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -9975,28 +9999,20 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Jubbonti / Wyost</t>
+          <t>Kauliv</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Theramex / Strides</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
       <c r="M115" s="2" t="inlineStr"/>
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr"/>
@@ -10004,85 +10020,87 @@
       <c r="Q115" s="2" t="inlineStr"/>
       <c r="R115" s="2" t="inlineStr"/>
       <c r="S115" s="2" t="inlineStr"/>
-      <c r="T115" s="2" t="inlineStr">
-        <is>
-          <t>SANDOZ</t>
-        </is>
-      </c>
-      <c r="U115" s="2" t="inlineStr">
-        <is>
-          <t>3400930305867</t>
-        </is>
-      </c>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>DENOSUMAB</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>M05BX04</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>Os / oncologie</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>mixte</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Obodence / Xbryk</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q116" s="2" t="inlineStr"/>
-      <c r="R116" s="2" t="inlineStr"/>
-      <c r="S116" s="2" t="inlineStr"/>
-      <c r="T116" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG BIOEPIS NL B.V.</t>
-        </is>
-      </c>
-      <c r="U116" s="2" t="inlineStr">
-        <is>
-          <t>3400930318485, 3400930318515</t>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Princeps</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Prolia / Xgeva</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr"/>
+      <c r="J116" s="5" t="inlineStr"/>
+      <c r="K116" s="5" t="inlineStr"/>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="n">
+        <v>333737</v>
+      </c>
+      <c r="N116" s="5" t="n">
+        <v>72539859.55</v>
+      </c>
+      <c r="O116" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="P116" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q116" s="5" t="n">
+        <v>144.79</v>
+      </c>
+      <c r="R116" s="5" t="n">
+        <v>139.16</v>
+      </c>
+      <c r="S116" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T116" s="5" t="inlineStr">
+        <is>
+          <t>AMGEN SAS</t>
+        </is>
+      </c>
+      <c r="U116" s="5" t="inlineStr">
+        <is>
+          <t>3400949285785, 3400921725384, 3400930289907</t>
         </is>
       </c>
     </row>
@@ -10119,19 +10137,23 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Stoboclo / Osenvelt</t>
+          <t>Jubbonti / Wyost</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
@@ -10140,20 +10162,18 @@
       <c r="M117" s="2" t="inlineStr"/>
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr"/>
-      <c r="P117" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="P117" s="2" t="inlineStr"/>
       <c r="Q117" s="2" t="inlineStr"/>
       <c r="R117" s="2" t="inlineStr"/>
       <c r="S117" s="2" t="inlineStr"/>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>CELLTRION HEALT</t>
+          <t>SANDOZ</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
         <is>
-          <t>3400930310120, 3400930310212</t>
+          <t>3400930305867, 3400930305874</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10210,12 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Osvyrti / Jubereq</t>
+          <t>Obodence / Xbryk</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Accord</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
@@ -10203,16 +10223,30 @@
       </c>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="M118" s="2" t="inlineStr"/>
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr"/>
-      <c r="P118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="Q118" s="2" t="inlineStr"/>
       <c r="R118" s="2" t="inlineStr"/>
       <c r="S118" s="2" t="inlineStr"/>
-      <c r="T118" s="2" t="inlineStr"/>
-      <c r="U118" s="2" t="inlineStr"/>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG BIOEPIS NL B.V.</t>
+        </is>
+      </c>
+      <c r="U118" s="2" t="inlineStr">
+        <is>
+          <t>3400930318485, 3400930318515</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -10247,12 +10281,12 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Izamby / Denbrayce</t>
+          <t>Stoboclo / Osenvelt</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>mAbxience</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
@@ -10260,16 +10294,30 @@
       </c>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="M119" s="2" t="inlineStr"/>
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr"/>
-      <c r="P119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="Q119" s="2" t="inlineStr"/>
       <c r="R119" s="2" t="inlineStr"/>
       <c r="S119" s="2" t="inlineStr"/>
-      <c r="T119" s="2" t="inlineStr"/>
-      <c r="U119" s="2" t="inlineStr"/>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>CELLTRION HEALT</t>
+        </is>
+      </c>
+      <c r="U119" s="2" t="inlineStr">
+        <is>
+          <t>3400930310120, 3400930310212</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -10304,12 +10352,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Conexxence / Bomyntra</t>
+          <t>Osvyrti / Jubereq</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Accord</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -10317,30 +10365,16 @@
       </c>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="L120" s="2" t="inlineStr"/>
       <c r="M120" s="2" t="inlineStr"/>
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr"/>
-      <c r="P120" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="P120" s="2" t="inlineStr"/>
       <c r="Q120" s="2" t="inlineStr"/>
       <c r="R120" s="2" t="inlineStr"/>
       <c r="S120" s="2" t="inlineStr"/>
-      <c r="T120" s="2" t="inlineStr">
-        <is>
-          <t>FRESENIUS KABI</t>
-        </is>
-      </c>
-      <c r="U120" s="2" t="inlineStr">
-        <is>
-          <t>3400930322260, 3400930322277</t>
-        </is>
-      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -10375,12 +10409,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Bildyos / Bilprevda</t>
+          <t>Izamby / Denbrayce</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Organon / Henlius</t>
+          <t>mAbxience</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
@@ -10432,12 +10466,12 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Kefdensis / Zvogra</t>
+          <t>Conexxence / Bomyntra</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Stada / Alvotech</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -10445,16 +10479,30 @@
       </c>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="M122" s="2" t="inlineStr"/>
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr"/>
-      <c r="P122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="Q122" s="2" t="inlineStr"/>
       <c r="R122" s="2" t="inlineStr"/>
       <c r="S122" s="2" t="inlineStr"/>
-      <c r="T122" s="2" t="inlineStr"/>
-      <c r="U122" s="2" t="inlineStr"/>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>FRESENIUS KABI</t>
+        </is>
+      </c>
+      <c r="U122" s="2" t="inlineStr">
+        <is>
+          <t>3400930322260, 3400930322277</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -10489,27 +10537,19 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Ponlimsi / Degevma</t>
+          <t>Bildyos / Bilprevda</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Organon / Henlius</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
       <c r="M123" s="2" t="inlineStr"/>
       <c r="N123" s="2" t="inlineStr"/>
@@ -10522,104 +10562,86 @@
       <c r="U123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>ENOXAPARINE</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>B01AB05</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>Anticoagulant (HBPM)</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>ville</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>Princeps</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>Lovenox</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="inlineStr">
-        <is>
-          <t>Sanofi</t>
-        </is>
-      </c>
-      <c r="I124" s="5" t="inlineStr"/>
-      <c r="J124" s="5" t="inlineStr"/>
-      <c r="K124" s="5" t="inlineStr"/>
-      <c r="L124" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M124" s="5" t="n">
-        <v>2192637</v>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v>52413671.26</v>
-      </c>
-      <c r="O124" s="5" t="inlineStr"/>
-      <c r="P124" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="Q124" s="5" t="inlineStr"/>
-      <c r="R124" s="5" t="inlineStr"/>
-      <c r="S124" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="T124" s="5" t="inlineStr">
-        <is>
-          <t>SANOFI AVENTI.F</t>
-        </is>
-      </c>
-      <c r="U124" s="5" t="inlineStr">
-        <is>
-          <t>3400930192948, 3400930193013, 3400936468375, 3400936468436, 3400936468665, 3400936468726, 3400936468955, 3400936469037, 3400936469266, 3400936469327, 3400936469495</t>
-        </is>
-      </c>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>DENOSUMAB</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>M05BX04</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Os / oncologie</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>mixte</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Kefdensis / Zvogra</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Stada / Alvotech</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ENOXAPARINE</t>
+          <t>DENOSUMAB</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>B01AB05</t>
+          <t>M05BX04</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Anticoagulant (HBPM)</t>
+          <t>Os / oncologie</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>OUI</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>ville</t>
+          <t>mixte</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -10629,110 +10651,112 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Inhixa</t>
+          <t>Ponlimsi / Degevma</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Techdow</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr"/>
+        <v>2025</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>936311</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>20806797</v>
-      </c>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr"/>
-      <c r="P125" s="2" t="n">
-        <v>38</v>
-      </c>
+      <c r="P125" s="2" t="inlineStr"/>
       <c r="Q125" s="2" t="inlineStr"/>
       <c r="R125" s="2" t="inlineStr"/>
-      <c r="S125" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="T125" s="2" t="inlineStr">
-        <is>
-          <t>BIOGARAN / VIATRIS SANTE</t>
-        </is>
-      </c>
-      <c r="U125" s="2" t="inlineStr">
-        <is>
-          <t>3400930129739, 3400930129746, 3400930129753, 3400930129760, 3400930129777, 3400930129784, 3400930129791, 3400930129807, 3400930129814</t>
-        </is>
-      </c>
+      <c r="S125" s="2" t="inlineStr"/>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>ENOXAPARINE</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>B01AB05</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>Anticoagulant (HBPM)</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
         <is>
           <t>ville</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>Biosimilaire</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Ghemaxan</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>Techdow</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr"/>
-      <c r="N126" s="2" t="inlineStr"/>
-      <c r="O126" s="2" t="inlineStr"/>
-      <c r="P126" s="2" t="inlineStr"/>
-      <c r="Q126" s="2" t="inlineStr"/>
-      <c r="R126" s="2" t="inlineStr"/>
-      <c r="S126" s="2" t="inlineStr"/>
-      <c r="T126" s="2" t="inlineStr"/>
-      <c r="U126" s="2" t="inlineStr"/>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Princeps</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Lovenox</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>Sanofi</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr"/>
+      <c r="J126" s="5" t="inlineStr"/>
+      <c r="K126" s="5" t="inlineStr"/>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M126" s="5" t="n">
+        <v>2192637</v>
+      </c>
+      <c r="N126" s="5" t="n">
+        <v>52413671.26</v>
+      </c>
+      <c r="O126" s="5" t="inlineStr"/>
+      <c r="P126" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q126" s="5" t="inlineStr"/>
+      <c r="R126" s="5" t="inlineStr"/>
+      <c r="S126" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="T126" s="5" t="inlineStr">
+        <is>
+          <t>SANOFI AVENTI.F</t>
+        </is>
+      </c>
+      <c r="U126" s="5" t="inlineStr">
+        <is>
+          <t>3400930192948, 3400930193013, 3400936468375, 3400936468436, 3400936468665, 3400936468726, 3400936468955, 3400936469037, 3400936469266, 3400936469327, 3400936469495</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -10767,125 +10791,125 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Crusia (Becat)</t>
+          <t>Inhixa</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Rovi</t>
+          <t>Techdow</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="inlineStr"/>
-      <c r="N127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>936311</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>20806797</v>
+      </c>
       <c r="O127" s="2" t="inlineStr"/>
-      <c r="P127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="n">
+        <v>38</v>
+      </c>
       <c r="Q127" s="2" t="inlineStr"/>
       <c r="R127" s="2" t="inlineStr"/>
-      <c r="S127" s="2" t="inlineStr"/>
-      <c r="T127" s="2" t="inlineStr"/>
-      <c r="U127" s="2" t="inlineStr"/>
+      <c r="S127" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>BIOGARAN / VIATRIS SANTE</t>
+        </is>
+      </c>
+      <c r="U127" s="2" t="inlineStr">
+        <is>
+          <t>3400930129739, 3400930129746, 3400930129753, 3400930129760, 3400930129777, 3400930129784, 3400930129791, 3400930129807, 3400930129814</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>FOLLITROPINE ALFA</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>G03GA05</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>AMP (stimulation ovarienne)</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>ENOXAPARINE</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>B01AB05</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Anticoagulant (HBPM)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>ville</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>Princeps</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>Gonal-F</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>Merck Serono</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr"/>
-      <c r="J128" s="5" t="inlineStr"/>
-      <c r="K128" s="5" t="inlineStr"/>
-      <c r="L128" s="5" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M128" s="5" t="n">
-        <v>176380</v>
-      </c>
-      <c r="N128" s="5" t="n">
-        <v>28097262.5</v>
-      </c>
-      <c r="O128" s="5" t="n">
-        <v>157</v>
-      </c>
-      <c r="P128" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q128" s="5" t="n">
-        <v>188.17</v>
-      </c>
-      <c r="R128" s="5" t="n">
-        <v>180.85</v>
-      </c>
-      <c r="S128" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T128" s="5" t="inlineStr">
-        <is>
-          <t>MERCK SERONO</t>
-        </is>
-      </c>
-      <c r="U128" s="5" t="inlineStr">
-        <is>
-          <t>3400936348110, 3400930212653, 3400935780188, 3400936347977, 3400936348059</t>
-        </is>
-      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Ghemaxan</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Techdow</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>FOLLITROPINE ALFA</t>
+          <t>ENOXAPARINE</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>G03GA05</t>
+          <t>B01AB05</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>AMP (stimulation ovarienne)</t>
+          <t>Anticoagulant (HBPM)</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -10905,72 +10929,44 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Ovaleap</t>
+          <t>Crusia (Becat)</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Theramex / Teva</t>
+          <t>Rovi</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>71648</v>
-      </c>
-      <c r="N129" s="2" t="n">
-        <v>8294038.51</v>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
       <c r="O129" s="2" t="inlineStr"/>
-      <c r="P129" s="2" t="n">
-        <v>24</v>
-      </c>
+      <c r="P129" s="2" t="inlineStr"/>
       <c r="Q129" s="2" t="inlineStr"/>
       <c r="R129" s="2" t="inlineStr"/>
-      <c r="S129" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T129" s="2" t="inlineStr">
-        <is>
-          <t>THERAMEX FRANCE</t>
-        </is>
-      </c>
-      <c r="U129" s="2" t="inlineStr">
-        <is>
-          <t>3400927903021, 3400927903199, 3400927903250</t>
-        </is>
-      </c>
+      <c r="S129" s="2" t="inlineStr"/>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FOLLITROPINE ALFA</t>
+          <t>ENOXAPARINE</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>G03GA05</t>
+          <t>B01AB05</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>AMP (stimulation ovarienne)</t>
+          <t>Anticoagulant (HBPM)</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -10990,16 +10986,16 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Bemfola</t>
+          <t>Enoxaparine Arrow</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Gedeon Richter / Finox</t>
+          <t>Arrow / Apotex</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
@@ -11009,105 +11005,107 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>476319</v>
+        <v>7228</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>16680985.61</v>
+        <v>218456.98</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
-      <c r="P130" s="2" t="n">
-        <v>122</v>
-      </c>
+      <c r="P130" s="2" t="inlineStr"/>
       <c r="Q130" s="2" t="inlineStr"/>
       <c r="R130" s="2" t="inlineStr"/>
-      <c r="S130" s="2" t="n">
-        <v>26</v>
-      </c>
+      <c r="S130" s="2" t="inlineStr"/>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>GEDEON RICHTER</t>
+          <t>ARROW GENERIQUE</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
         <is>
-          <t>3400927939099, 3400927939150, 3400927939211, 3400927939389, 3400927939440</t>
+          <t>3400930199671, 3400930201749, 3400930201763</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>SOMATROPINE</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>H01AC01</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>Endocrino (hormone de croissance)</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>ENOXAPARINE</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>B01AB05</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Anticoagulant (HBPM)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>ville</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>Princeps</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>Genotropin / Humatrope</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>Pfizer / Lilly</t>
-        </is>
-      </c>
-      <c r="I131" s="5" t="inlineStr"/>
-      <c r="J131" s="5" t="inlineStr"/>
-      <c r="K131" s="5" t="inlineStr"/>
-      <c r="L131" s="5" t="inlineStr"/>
-      <c r="M131" s="5" t="inlineStr"/>
-      <c r="N131" s="5" t="inlineStr"/>
-      <c r="O131" s="5" t="inlineStr"/>
-      <c r="P131" s="5" t="inlineStr"/>
-      <c r="Q131" s="5" t="inlineStr"/>
-      <c r="R131" s="5" t="inlineStr"/>
-      <c r="S131" s="5" t="inlineStr"/>
-      <c r="T131" s="5" t="inlineStr"/>
-      <c r="U131" s="5" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Enoxaparine Biogaran</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Biogaran</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr"/>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr"/>
+      <c r="R131" s="2" t="inlineStr"/>
+      <c r="S131" s="2" t="inlineStr"/>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>SOMATROPINE</t>
+          <t>ENOXAPARINE</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>H01AC01</t>
+          <t>B01AB05</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Endocrino (hormone de croissance)</t>
+          <t>Anticoagulant (HBPM)</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>OUI</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -11122,84 +11120,62 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Omnitrope</t>
+          <t>Enoxaparine Teva</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr"/>
+        <v>2021</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>90785</v>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>43284279.99</v>
-      </c>
-      <c r="O132" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="P132" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q132" s="2" t="n">
-        <v>282.56</v>
-      </c>
-      <c r="R132" s="2" t="n">
-        <v>271.57</v>
-      </c>
-      <c r="S132" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T132" s="2" t="inlineStr">
-        <is>
-          <t>SANDOZ</t>
-        </is>
-      </c>
-      <c r="U132" s="2" t="inlineStr">
-        <is>
-          <t>3400921687781, 3400921687842, 3400921687903, 3400927552403, 3400927552571, 3400927552632, 3400927552861, 3400927552922, 3400927553004</t>
-        </is>
-      </c>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr"/>
+      <c r="R132" s="2" t="inlineStr"/>
+      <c r="S132" s="2" t="inlineStr"/>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>ECULIZUMAB</t>
+          <t>FOLLITROPINE ALFA</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>L04AJ01</t>
+          <t>G03GA05</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Maladies rares (anti-C5)</t>
+          <t>AMP (stimulation ovarienne)</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>OUI</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>hopital</t>
+          <t>ville</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -11209,52 +11185,78 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>Soliris</t>
+          <t>Gonal-F</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>Alexion / AstraZeneca</t>
+          <t>Merck Serono</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr"/>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="5" t="inlineStr"/>
-      <c r="L133" s="5" t="inlineStr"/>
-      <c r="M133" s="5" t="inlineStr"/>
-      <c r="N133" s="5" t="inlineStr"/>
-      <c r="O133" s="5" t="inlineStr"/>
-      <c r="P133" s="5" t="inlineStr"/>
-      <c r="Q133" s="5" t="inlineStr"/>
-      <c r="R133" s="5" t="inlineStr"/>
-      <c r="S133" s="5" t="inlineStr"/>
-      <c r="T133" s="5" t="inlineStr"/>
-      <c r="U133" s="5" t="inlineStr"/>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="n">
+        <v>176380</v>
+      </c>
+      <c r="N133" s="5" t="n">
+        <v>28097262.5</v>
+      </c>
+      <c r="O133" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="P133" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q133" s="5" t="n">
+        <v>188.17</v>
+      </c>
+      <c r="R133" s="5" t="n">
+        <v>180.85</v>
+      </c>
+      <c r="S133" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T133" s="5" t="inlineStr">
+        <is>
+          <t>MERCK SERONO</t>
+        </is>
+      </c>
+      <c r="U133" s="5" t="inlineStr">
+        <is>
+          <t>3400936348110, 3400930212653, 3400935780188, 3400936347977, 3400936348059</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ECULIZUMAB</t>
+          <t>FOLLITROPINE ALFA</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>L04AJ01</t>
+          <t>G03GA05</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Maladies rares (anti-C5)</t>
+          <t>AMP (stimulation ovarienne)</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>OUI</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>hopital</t>
+          <t>ville</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -11264,54 +11266,82 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Bekemv</t>
+          <t>Ovaleap</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Theramex / Teva</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
-      <c r="N134" s="2" t="inlineStr"/>
+        <v>2013</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>71648</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>8294038.51</v>
+      </c>
       <c r="O134" s="2" t="inlineStr"/>
-      <c r="P134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="n">
+        <v>24</v>
+      </c>
       <c r="Q134" s="2" t="inlineStr"/>
       <c r="R134" s="2" t="inlineStr"/>
-      <c r="S134" s="2" t="inlineStr"/>
-      <c r="T134" s="2" t="inlineStr"/>
-      <c r="U134" s="2" t="inlineStr"/>
+      <c r="S134" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>THERAMEX FRANCE</t>
+        </is>
+      </c>
+      <c r="U134" s="2" t="inlineStr">
+        <is>
+          <t>3400927903021, 3400927903199, 3400927903250</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>ECULIZUMAB</t>
+          <t>FOLLITROPINE ALFA</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>L04AJ01</t>
+          <t>G03GA05</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Maladies rares (anti-C5)</t>
+          <t>AMP (stimulation ovarienne)</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>OUI</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>hopital</t>
+          <t>ville</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -11321,29 +11351,360 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Epysqli</t>
+          <t>Bemfola</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Gedeon Richter / Finox</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="2" t="inlineStr"/>
-      <c r="N135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>476319</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>16680985.61</v>
+      </c>
       <c r="O135" s="2" t="inlineStr"/>
-      <c r="P135" s="2" t="inlineStr"/>
+      <c r="P135" s="2" t="n">
+        <v>122</v>
+      </c>
       <c r="Q135" s="2" t="inlineStr"/>
       <c r="R135" s="2" t="inlineStr"/>
-      <c r="S135" s="2" t="inlineStr"/>
-      <c r="T135" s="2" t="inlineStr"/>
-      <c r="U135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>GEDEON RICHTER</t>
+        </is>
+      </c>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>3400927939099, 3400927939150, 3400927939211, 3400927939389, 3400927939440</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>SOMATROPINE</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>H01AC01</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Endocrino (hormone de croissance)</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>ville</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Princeps</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Genotropin / Humatrope</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>Pfizer / Lilly</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr"/>
+      <c r="J136" s="5" t="inlineStr"/>
+      <c r="K136" s="5" t="inlineStr"/>
+      <c r="L136" s="5" t="inlineStr"/>
+      <c r="M136" s="5" t="inlineStr"/>
+      <c r="N136" s="5" t="inlineStr"/>
+      <c r="O136" s="5" t="inlineStr"/>
+      <c r="P136" s="5" t="inlineStr"/>
+      <c r="Q136" s="5" t="inlineStr"/>
+      <c r="R136" s="5" t="inlineStr"/>
+      <c r="S136" s="5" t="inlineStr"/>
+      <c r="T136" s="5" t="inlineStr"/>
+      <c r="U136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>SOMATROPINE</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>H01AC01</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Endocrino (hormone de croissance)</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>ville</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Omnitrope</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Sandoz</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>90785</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>43284279.99</v>
+      </c>
+      <c r="O137" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="P137" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q137" s="2" t="n">
+        <v>282.56</v>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>271.57</v>
+      </c>
+      <c r="S137" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>SANDOZ</t>
+        </is>
+      </c>
+      <c r="U137" s="2" t="inlineStr">
+        <is>
+          <t>3400921687781, 3400921687842, 3400921687903, 3400927552403, 3400927552571, 3400927552632, 3400927552861, 3400927552922, 3400927553004</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>ECULIZUMAB</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>L04AJ01</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Maladies rares (anti-C5)</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>hopital</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Princeps</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>Soliris</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>Alexion / AstraZeneca</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr"/>
+      <c r="J138" s="5" t="inlineStr"/>
+      <c r="K138" s="5" t="inlineStr"/>
+      <c r="L138" s="5" t="inlineStr"/>
+      <c r="M138" s="5" t="inlineStr"/>
+      <c r="N138" s="5" t="inlineStr"/>
+      <c r="O138" s="5" t="inlineStr"/>
+      <c r="P138" s="5" t="inlineStr"/>
+      <c r="Q138" s="5" t="inlineStr"/>
+      <c r="R138" s="5" t="inlineStr"/>
+      <c r="S138" s="5" t="inlineStr"/>
+      <c r="T138" s="5" t="inlineStr"/>
+      <c r="U138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>ECULIZUMAB</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>L04AJ01</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Maladies rares (anti-C5)</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>hopital</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Bekemv</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr"/>
+      <c r="R139" s="2" t="inlineStr"/>
+      <c r="S139" s="2" t="inlineStr"/>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>ECULIZUMAB</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>L04AJ01</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Maladies rares (anti-C5)</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>hopital</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Biosimilaire</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Epysqli</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr"/>
+      <c r="R140" s="2" t="inlineStr"/>
+      <c r="S140" s="2" t="inlineStr"/>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11445,22 +11806,22 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>ADALIMUMAB</t>
+          <t>ENOXAPARINE</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>L04AB04</t>
+          <t>B01AB05</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Rhumato / gastro / dermato</t>
+          <t>Anticoagulant (HBPM)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Humira</t>
+          <t>Lovenox</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -11469,7 +11830,7 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -11478,44 +11839,44 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>EG LABO, Stada / Alvotech</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>798009</v>
+        <v>943539</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>FILGRASTIM</t>
+          <t>ADALIMUMAB</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>L03AA02</t>
+          <t>L04AB04</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Soins de support (G-CSF)</t>
+          <t>Rhumato / gastro / dermato</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Neupogen</t>
+          <t>Humira</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -11524,44 +11885,44 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>TEVA SANTE, Teva</t>
+          <t>Amgen, EG LABO, Stada / Alvotech</t>
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>652539</v>
+        <v>798009</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>FOLLITROPINE ALFA</t>
+          <t>FILGRASTIM</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>G03GA05</t>
+          <t>L03AA02</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>AMP (stimulation ovarienne)</t>
+          <t>Soins de support (G-CSF)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Gonal-F</t>
+          <t>Neupogen</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -11570,44 +11931,44 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Theramex / Teva</t>
+          <t>TEVA SANTE, Teva, Teva / ratiopharm</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>547967</v>
+        <v>748081</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>PEGFILGRASTIM</t>
+          <t>FOLLITROPINE ALFA</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>L03AA13</t>
+          <t>G03GA05</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Soins de support (G-CSF)</t>
+          <t>AMP (stimulation ovarienne)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Neulasta</t>
+          <t>Gonal-F</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -11616,44 +11977,44 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Fresenius Kabi, Mundipharma, TEVA SANTE, ZENTIVA FRANCE</t>
+          <t>Theramex / Teva</t>
         </is>
       </c>
       <c r="I8" s="7" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>305141</v>
+        <v>547967</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>TERIPARATIDE</t>
+          <t>PEGFILGRASTIM</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>H05AA02</t>
+          <t>L03AA13</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Ostéoporose</t>
+          <t>Soins de support (G-CSF)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Forstéo</t>
+          <t>Neulasta</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2022-04-12</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -11662,44 +12023,44 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>EG, EG LABO, Stada</t>
+          <t>Fresenius Kabi, Mundipharma, TEVA SANTE, ZENTIVA FRANCE</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>91324</v>
+        <v>305141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>RANIBIZUMAB</t>
+          <t>TERIPARATIDE</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>S01LA04</t>
+          <t>H05AA02</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Ophtalmo (intravitréen)</t>
+          <t>Ostéoporose</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Lucentis</t>
+          <t>Forstéo</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>groupe historique</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -11708,106 +12069,106 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>EG LABO, Stada / Xbrane, TEVA SANTE, Teva / Bioeq</t>
+          <t>EG, EG LABO, Stada</t>
         </is>
       </c>
       <c r="I10" s="7" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>53846</v>
+        <v>91324</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>RANIBIZUMAB</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>S01LA04</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Ophtalmo (intravitréen)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Lucentis</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>groupe historique</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>EG LABO, Stada / Xbrane, TEVA SANTE, Teva / Bioeq</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>53846</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>USTEKINUMAB</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>L04AC05</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Dermato / rhumato / gastro</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Stelara</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>EG LABO, Stada / Alvotech</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I12" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J12" s="7" t="n">
         <v>39122</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>ENOXAPARINE</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>B01AB05</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Anticoagulant (HBPM)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Lovenox</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>936311</v>
       </c>
     </row>
     <row r="13">

--- a/base-biosimilaires.xlsx
+++ b/base-biosimilaires.xlsx
@@ -2244,10 +2244,10 @@
       </c>
       <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="n">
-        <v>354.74</v>
+        <v>394.08</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>340.94</v>
+        <v>378.75</v>
       </c>
       <c r="S3" s="5" t="n">
         <v>16</v>
@@ -2335,10 +2335,10 @@
         <v>13</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>197.36</v>
+        <v>354.74</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>189.68</v>
+        <v>340.94</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>10</v>
@@ -2585,8 +2585,12 @@
       <c r="P7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>340.94</v>
+      </c>
       <c r="S7" s="2" t="n">
         <v>6</v>
       </c>
@@ -2660,8 +2664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>340.94</v>
+      </c>
       <c r="S8" s="2" t="n">
         <v>2</v>
       </c>
@@ -2735,8 +2743,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>340.94</v>
+      </c>
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
@@ -2897,8 +2909,12 @@
       <c r="P11" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>340.94</v>
+      </c>
       <c r="S11" s="2" t="n">
         <v>1</v>
       </c>
@@ -2978,8 +2994,12 @@
       <c r="P12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>340.94</v>
+      </c>
       <c r="S12" s="2" t="n">
         <v>2</v>
       </c>
@@ -3061,8 +3081,12 @@
       <c r="P13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Q13" s="5" t="inlineStr"/>
-      <c r="R13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="n">
+        <v>441.16</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>424</v>
+      </c>
       <c r="S13" s="5" t="n">
         <v>5</v>
       </c>
@@ -3223,8 +3247,12 @@
       <c r="P15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="n">
+        <v>441.16</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>424</v>
+      </c>
       <c r="S15" s="2" t="n">
         <v>3</v>
       </c>
@@ -3696,8 +3724,12 @@
       <c r="P22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="n">
+        <v>477.98</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>458.48</v>
+      </c>
       <c r="S22" s="5" t="n">
         <v>11</v>
       </c>
@@ -3883,8 +3915,12 @@
       </c>
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="n">
+        <v>1393.18</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>1373.68</v>
+      </c>
       <c r="S25" s="5" t="n">
         <v>8</v>
       </c>
@@ -4045,8 +4081,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="n">
+        <v>1053.17</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>1033.67</v>
+      </c>
       <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
@@ -4122,8 +4162,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="n">
+        <v>1053.17</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>1033.67</v>
+      </c>
       <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
@@ -4197,8 +4241,12 @@
       <c r="P29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="n">
+        <v>1053.17</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>1033.67</v>
+      </c>
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
@@ -4272,8 +4320,12 @@
       <c r="P30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="n">
+        <v>1053.17</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>1033.67</v>
+      </c>
       <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
@@ -4457,8 +4509,12 @@
       </c>
       <c r="O33" s="5" t="inlineStr"/>
       <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="n">
+        <v>534.39</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>514.89</v>
+      </c>
       <c r="S33" s="5" t="n">
         <v>7</v>
       </c>
@@ -4532,8 +4588,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="n">
+        <v>449.93</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>432.43</v>
+      </c>
       <c r="S34" s="2" t="n">
         <v>1</v>
       </c>
@@ -4605,8 +4665,12 @@
       <c r="P35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>108.56</v>
+      </c>
       <c r="S35" s="2" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
@@ -6347,8 +6411,12 @@
       <c r="P65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" s="5" t="inlineStr"/>
-      <c r="R65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="R65" s="5" t="n">
+        <v>52.5</v>
+      </c>
       <c r="S65" s="5" t="n">
         <v>1</v>
       </c>
@@ -6519,8 +6587,12 @@
       <c r="P67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" s="2" t="inlineStr"/>
-      <c r="R67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>52.5</v>
+      </c>
       <c r="S67" s="2" t="n">
         <v>3</v>
       </c>
@@ -6602,8 +6674,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>52.5</v>
+      </c>
       <c r="S68" s="2" t="n">
         <v>5</v>
       </c>
@@ -6675,8 +6751,12 @@
       <c r="P69" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>52.5</v>
+      </c>
       <c r="S69" s="2" t="n">
         <v>7</v>
       </c>
@@ -6949,8 +7029,12 @@
       </c>
       <c r="O73" s="5" t="inlineStr"/>
       <c r="P73" s="5" t="inlineStr"/>
-      <c r="Q73" s="5" t="inlineStr"/>
-      <c r="R73" s="5" t="inlineStr"/>
+      <c r="Q73" s="5" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="R73" s="5" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S73" s="5" t="n">
         <v>1</v>
       </c>
@@ -7028,8 +7112,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S74" s="2" t="n">
         <v>4</v>
       </c>
@@ -7105,8 +7193,12 @@
       <c r="P75" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="Q75" s="2" t="inlineStr"/>
-      <c r="R75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>349.25</v>
+      </c>
       <c r="S75" s="2" t="n">
         <v>2</v>
       </c>
@@ -7182,8 +7274,12 @@
       <c r="P76" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="Q76" s="2" t="inlineStr"/>
-      <c r="R76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S76" s="2" t="n">
         <v>2</v>
       </c>
@@ -7263,8 +7359,12 @@
       <c r="P77" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="Q77" s="2" t="inlineStr"/>
-      <c r="R77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S77" s="2" t="n">
         <v>2</v>
       </c>
@@ -7431,8 +7531,12 @@
       <c r="P79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" s="2" t="inlineStr"/>
-      <c r="R79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S79" s="2" t="inlineStr"/>
       <c r="T79" s="2" t="inlineStr">
         <is>
@@ -7504,8 +7608,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr"/>
-      <c r="R80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S80" s="2" t="n">
         <v>3</v>
       </c>
@@ -7587,8 +7695,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr"/>
-      <c r="Q81" s="2" t="inlineStr"/>
-      <c r="R81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S81" s="2" t="n">
         <v>1</v>
       </c>
@@ -8305,8 +8417,12 @@
       <c r="P91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" s="2" t="inlineStr"/>
-      <c r="R91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>31.36</v>
+      </c>
       <c r="S91" s="2" t="inlineStr"/>
       <c r="T91" s="2" t="inlineStr">
         <is>
@@ -8379,10 +8495,10 @@
       </c>
       <c r="P92" s="5" t="inlineStr"/>
       <c r="Q92" s="5" t="n">
-        <v>11.78</v>
+        <v>20.39</v>
       </c>
       <c r="R92" s="5" t="n">
-        <v>11.32</v>
+        <v>19.59</v>
       </c>
       <c r="S92" s="5" t="n">
         <v>186</v>
@@ -8578,10 +8694,10 @@
         <v>31</v>
       </c>
       <c r="Q95" s="5" t="n">
-        <v>13.14</v>
+        <v>25.97</v>
       </c>
       <c r="R95" s="5" t="n">
-        <v>12.63</v>
+        <v>24.96</v>
       </c>
       <c r="S95" s="5" t="n">
         <v>97</v>
@@ -8794,8 +8910,12 @@
       <c r="P98" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>277.23</v>
+      </c>
       <c r="S98" s="2" t="n">
         <v>1</v>
       </c>
@@ -8877,8 +8997,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr"/>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>277.23</v>
+      </c>
       <c r="S99" s="2" t="n">
         <v>2</v>
       </c>
@@ -8960,8 +9084,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr"/>
       <c r="P100" s="2" t="inlineStr"/>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>277.23</v>
+      </c>
       <c r="S100" s="2" t="inlineStr"/>
       <c r="T100" s="2" t="inlineStr">
         <is>
@@ -9031,8 +9159,12 @@
       <c r="P101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>277.23</v>
+      </c>
       <c r="S101" s="2" t="inlineStr"/>
       <c r="T101" s="2" t="inlineStr">
         <is>
@@ -9199,8 +9331,12 @@
       <c r="P103" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="Q103" s="2" t="inlineStr"/>
-      <c r="R103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="n">
+        <v>227.38</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>218.53</v>
+      </c>
       <c r="S103" s="2" t="n">
         <v>1</v>
       </c>
@@ -9443,8 +9579,12 @@
       <c r="P107" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" s="2" t="inlineStr"/>
-      <c r="R107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="n">
+        <v>227.38</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>218.53</v>
+      </c>
       <c r="S107" s="2" t="inlineStr"/>
       <c r="T107" s="2" t="inlineStr">
         <is>
@@ -9724,9 +9864,11 @@
         <v>18</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="R111" s="2" t="inlineStr"/>
+        <v>185.33</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>178.12</v>
+      </c>
       <c r="S111" s="2" t="n">
         <v>3</v>
       </c>
@@ -9800,8 +9942,12 @@
       </c>
       <c r="O112" s="2" t="inlineStr"/>
       <c r="P112" s="2" t="inlineStr"/>
-      <c r="Q112" s="2" t="inlineStr"/>
-      <c r="R112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="n">
+        <v>185.33</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>178.12</v>
+      </c>
       <c r="S112" s="2" t="n">
         <v>1</v>
       </c>
@@ -9875,8 +10021,12 @@
       </c>
       <c r="O113" s="2" t="inlineStr"/>
       <c r="P113" s="2" t="inlineStr"/>
-      <c r="Q113" s="2" t="inlineStr"/>
-      <c r="R113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="n">
+        <v>185.33</v>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>178.12</v>
+      </c>
       <c r="S113" s="2" t="n">
         <v>1</v>
       </c>
@@ -9950,8 +10100,12 @@
       </c>
       <c r="O114" s="2" t="inlineStr"/>
       <c r="P114" s="2" t="inlineStr"/>
-      <c r="Q114" s="2" t="inlineStr"/>
-      <c r="R114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="n">
+        <v>185.96</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>178.73</v>
+      </c>
       <c r="S114" s="2" t="n">
         <v>1</v>
       </c>
@@ -10163,8 +10317,12 @@
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr"/>
       <c r="P117" s="2" t="inlineStr"/>
-      <c r="Q117" s="2" t="inlineStr"/>
-      <c r="R117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="R117" s="2" t="n">
+        <v>138.12</v>
+      </c>
       <c r="S117" s="2" t="inlineStr"/>
       <c r="T117" s="2" t="inlineStr">
         <is>
@@ -10234,8 +10392,12 @@
       <c r="P118" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" s="2" t="inlineStr"/>
-      <c r="R118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>138.12</v>
+      </c>
       <c r="S118" s="2" t="inlineStr"/>
       <c r="T118" s="2" t="inlineStr">
         <is>
@@ -10305,8 +10467,12 @@
       <c r="P119" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" s="2" t="inlineStr"/>
-      <c r="R119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>138.12</v>
+      </c>
       <c r="S119" s="2" t="inlineStr"/>
       <c r="T119" s="2" t="inlineStr">
         <is>
@@ -10490,8 +10656,12 @@
       <c r="P122" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q122" s="2" t="inlineStr"/>
-      <c r="R122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>138.12</v>
+      </c>
       <c r="S122" s="2" t="inlineStr"/>
       <c r="T122" s="2" t="inlineStr">
         <is>
@@ -10742,8 +10912,12 @@
       <c r="P126" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="Q126" s="5" t="inlineStr"/>
-      <c r="R126" s="5" t="inlineStr"/>
+      <c r="Q126" s="5" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="R126" s="5" t="n">
+        <v>22.43</v>
+      </c>
       <c r="S126" s="5" t="n">
         <v>63</v>
       </c>
@@ -10823,8 +10997,12 @@
       <c r="P127" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="Q127" s="2" t="inlineStr"/>
-      <c r="R127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>22.43</v>
+      </c>
       <c r="S127" s="2" t="n">
         <v>56</v>
       </c>
@@ -11012,8 +11190,12 @@
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr"/>
-      <c r="Q130" s="2" t="inlineStr"/>
-      <c r="R130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>43.11</v>
+      </c>
       <c r="S130" s="2" t="inlineStr"/>
       <c r="T130" s="2" t="inlineStr">
         <is>
@@ -11302,8 +11484,12 @@
       <c r="P134" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="Q134" s="2" t="inlineStr"/>
-      <c r="R134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="n">
+        <v>149.79</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>143.96</v>
+      </c>
       <c r="S134" s="2" t="n">
         <v>4</v>
       </c>
@@ -11379,8 +11565,12 @@
       <c r="P135" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="Q135" s="2" t="inlineStr"/>
-      <c r="R135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>12.53</v>
+      </c>
       <c r="S135" s="2" t="n">
         <v>26</v>
       </c>
